--- a/informes/pagosPendientes.xlsx
+++ b/informes/pagosPendientes.xlsx
@@ -277,7 +277,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1119970301" name="Picture">
+        <xdr:cNvPr id="969808003" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
@@ -422,7 +422,7 @@
       <c r="H5" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">miércoles 27 mayo 2026</t>
+            <t xml:space="preserve">domingo 31 mayo 2026</t>
           </r>
         </is>
       </c>
@@ -453,7 +453,7 @@
       <c r="O6" s="1" t="inlineStr"/>
       <c r="P6" s="1" t="inlineStr"/>
     </row>
-    <row r="7" customHeight="1" ht="45">
+    <row r="7" customHeight="1" ht="5">
       <c r="A7" s="1" t="inlineStr"/>
       <c r="B7" s="1" t="inlineStr"/>
       <c r="C7" s="1" t="inlineStr"/>
@@ -525,7 +525,7 @@
       <c r="C9" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Luis Fernández Torres</t>
+            <t xml:space="preserve">Laura Martín Santos</t>
           </r>
         </is>
       </c>
@@ -533,7 +533,7 @@
       <c r="E9" s="9" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">5/3/23, 0:00</t>
+            <t xml:space="preserve">31/05/26 0:00</t>
           </r>
         </is>
       </c>
@@ -541,7 +541,7 @@
       <c r="G9" s="9" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">45678912C</t>
+            <t xml:space="preserve">78912345D</t>
           </r>
         </is>
       </c>
@@ -550,7 +550,7 @@
       <c r="J9" s="9" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">30.0</t>
+            <t xml:space="preserve">150.0</t>
           </r>
         </is>
       </c>
@@ -567,71 +567,215 @@
       <c r="O9" s="1" t="inlineStr"/>
       <c r="P9" s="1" t="inlineStr"/>
     </row>
-    <row r="10" customHeight="1" ht="566">
+    <row r="10" customHeight="1" ht="30">
       <c r="A10" s="1" t="inlineStr"/>
       <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr"/>
-      <c r="D10" s="1" t="inlineStr"/>
-      <c r="E10" s="1" t="inlineStr"/>
-      <c r="F10" s="1" t="inlineStr"/>
-      <c r="G10" s="1" t="inlineStr"/>
-      <c r="H10" s="1" t="inlineStr"/>
-      <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr"/>
-      <c r="L10" s="1" t="inlineStr"/>
-      <c r="M10" s="1" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Diego Castillo </t>
+          </r>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">99001122H</t>
+          </r>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">150.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pendiente</t>
+          </r>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr"/>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
     </row>
-    <row r="11" customHeight="1" ht="20">
+    <row r="11" customHeight="1" ht="30">
       <c r="A11" s="1" t="inlineStr"/>
       <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr"/>
-      <c r="D11" s="1" t="inlineStr"/>
-      <c r="E11" s="1" t="inlineStr"/>
-      <c r="F11" s="1" t="inlineStr"/>
-      <c r="G11" s="1" t="inlineStr"/>
-      <c r="H11" s="1" t="inlineStr"/>
-      <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Page 1 de</t>
-          </r>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> 1</t>
-          </r>
-        </is>
-      </c>
-      <c r="N11" s="10" t="inlineStr"/>
-      <c r="O11" s="10" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Diego Castillo </t>
+          </r>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">99001122H</t>
+          </r>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr"/>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">150.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pendiente</t>
+          </r>
+        </is>
+      </c>
+      <c r="M11" s="9" t="inlineStr"/>
+      <c r="N11" s="1" t="inlineStr"/>
+      <c r="O11" s="1" t="inlineStr"/>
       <c r="P11" s="1" t="inlineStr"/>
     </row>
-    <row r="12" customHeight="1" ht="20">
+    <row r="12" customHeight="1" ht="30">
       <c r="A12" s="1" t="inlineStr"/>
       <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr"/>
-      <c r="D12" s="1" t="inlineStr"/>
-      <c r="E12" s="1" t="inlineStr"/>
-      <c r="F12" s="1" t="inlineStr"/>
-      <c r="G12" s="1" t="inlineStr"/>
-      <c r="H12" s="1" t="inlineStr"/>
-      <c r="I12" s="1" t="inlineStr"/>
-      <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr"/>
-      <c r="L12" s="1" t="inlineStr"/>
-      <c r="M12" s="1" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Diego Castillo </t>
+          </r>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/03/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">99001122H</t>
+          </r>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">150.0</t>
+          </r>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pendiente</t>
+          </r>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr"/>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
+    </row>
+    <row r="13" customHeight="1" ht="516">
+      <c r="A13" s="1" t="inlineStr"/>
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr"/>
+      <c r="D13" s="1" t="inlineStr"/>
+      <c r="E13" s="1" t="inlineStr"/>
+      <c r="F13" s="1" t="inlineStr"/>
+      <c r="G13" s="1" t="inlineStr"/>
+      <c r="H13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr"/>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
+      <c r="L13" s="1" t="inlineStr"/>
+      <c r="M13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr"/>
+      <c r="O13" s="1" t="inlineStr"/>
+      <c r="P13" s="1" t="inlineStr"/>
+    </row>
+    <row r="14" customHeight="1" ht="20">
+      <c r="A14" s="1" t="inlineStr"/>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr"/>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr"/>
+      <c r="F14" s="1" t="inlineStr"/>
+      <c r="G14" s="1" t="inlineStr"/>
+      <c r="H14" s="1" t="inlineStr"/>
+      <c r="I14" s="1" t="inlineStr"/>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Page 1 de</t>
+          </r>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> 1</t>
+          </r>
+        </is>
+      </c>
+      <c r="N14" s="10" t="inlineStr"/>
+      <c r="O14" s="10" t="inlineStr"/>
+      <c r="P14" s="1" t="inlineStr"/>
+    </row>
+    <row r="15" customHeight="1" ht="20">
+      <c r="A15" s="1" t="inlineStr"/>
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr"/>
+      <c r="D15" s="1" t="inlineStr"/>
+      <c r="E15" s="1" t="inlineStr"/>
+      <c r="F15" s="1" t="inlineStr"/>
+      <c r="G15" s="1" t="inlineStr"/>
+      <c r="H15" s="1" t="inlineStr"/>
+      <c r="I15" s="1" t="inlineStr"/>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
+      <c r="L15" s="1" t="inlineStr"/>
+      <c r="M15" s="1" t="inlineStr"/>
+      <c r="N15" s="1" t="inlineStr"/>
+      <c r="O15" s="1" t="inlineStr"/>
+      <c r="P15" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -649,8 +793,23 @@
     <mergeCell ref="G9:I9"/>
     <mergeCell ref="J9:K9"/>
     <mergeCell ref="L9:M9"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:O14"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="portrait" paperSize="9"/>
